--- a/output/2026-09-08_00_Croazia_Krapinsko-zagorska_Cleaning.xlsx
+++ b/output/2026-09-08_00_Croazia_Krapinsko-zagorska_Cleaning.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore/rivenditore B2B di utensili professionali e industriali (Makita, Bosch, Rems, Flex, DeWalt, Metabo); confermata vendita di aspiratori industriali nel catalogo online (es. Makita VC3011L, Stayer VAC2050C).</t>
+          <t>Distributore/rivenditore B2B di utensili professionali e industriali (Makita, Bosch, Rems, Flex, DeWalt, Metabo); confermata vendita di aspiratori industriali nel catalogo online (es. Makita VC3011L, Stayer VAC2050C). [DUPLICATO — vedi anche: 2026-09-07_23_Croazia_Zagrebacka_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
